--- a/data/outputSpecialityRpt/Aggregate/Consolidated_OutputSpecialityRpt.xlsx
+++ b/data/outputSpecialityRpt/Aggregate/Consolidated_OutputSpecialityRpt.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,11 +466,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TC111</t>
+          <t>TC10</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -491,39 +491,6 @@
         <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TC112</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>21</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
